--- a/src/ii_skills/shared/excel_templates/03_peer_benchmarking.xlsx
+++ b/src/ii_skills/shared/excel_templates/03_peer_benchmarking.xlsx
@@ -8,7 +8,6 @@
   </bookViews>
   <sheets>
     <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Peer_Benchmarking" sheetId="1" state="visible" r:id="rId1"/>
-    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Instructions" sheetId="2" state="visible" r:id="rId2"/>
   </sheets>
   <definedNames/>
   <calcPr calcId="124519" fullCalcOnLoad="1"/>
@@ -18,7 +17,7 @@
 <file path=xl/styles.xml><?xml version="1.0" encoding="utf-8"?>
 <styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
   <numFmts count="0"/>
-  <fonts count="3">
+  <fonts count="5">
     <font>
       <name val="Calibri"/>
       <family val="2"/>
@@ -28,14 +27,22 @@
     </font>
     <font>
       <b val="1"/>
+      <color rgb="0001395D"/>
+      <sz val="14"/>
+    </font>
+    <font>
+      <b val="1"/>
       <color rgb="00FFFFFF"/>
     </font>
     <font>
       <b val="1"/>
-      <sz val="14"/>
+    </font>
+    <font>
+      <b val="1"/>
+      <sz val="11"/>
     </font>
   </fonts>
-  <fills count="4">
+  <fills count="7">
     <fill>
       <patternFill/>
     </fill>
@@ -44,18 +51,36 @@
     </fill>
     <fill>
       <patternFill patternType="solid">
-        <fgColor rgb="004A4A4A"/>
-        <bgColor rgb="004A4A4A"/>
+        <fgColor rgb="0001395D"/>
+        <bgColor rgb="0001395D"/>
       </patternFill>
     </fill>
     <fill>
       <patternFill patternType="solid">
-        <fgColor rgb="00F0F0F0"/>
-        <bgColor rgb="00F0F0F0"/>
+        <fgColor rgb="00FFCDD2"/>
+        <bgColor rgb="00FFCDD2"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="00FFF9C4"/>
+        <bgColor rgb="00FFF9C4"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="00C8E6C9"/>
+        <bgColor rgb="00C8E6C9"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="0081C784"/>
+        <bgColor rgb="0081C784"/>
       </patternFill>
     </fill>
   </fills>
-  <borders count="2">
+  <borders count="1">
     <border>
       <left/>
       <right/>
@@ -63,24 +88,29 @@
       <bottom/>
       <diagonal/>
     </border>
-    <border>
-      <left style="thin"/>
-      <right style="thin"/>
-      <top style="thin"/>
-      <bottom style="thin"/>
-    </border>
   </borders>
   <cellStyleXfs count="1">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
   </cellStyleXfs>
-  <cellXfs count="5">
+  <cellXfs count="8">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
-    <xf numFmtId="0" fontId="1" fillId="2" borderId="0" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
-      <alignment horizontal="center"/>
+    <xf numFmtId="0" fontId="1" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
+    <xf numFmtId="0" fontId="2" fillId="2" borderId="0" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="center" vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="0" fillId="3" borderId="1" pivotButton="0" quotePrefix="0" xfId="0"/>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="1" pivotButton="0" quotePrefix="0" xfId="0"/>
-    <xf numFmtId="0" fontId="2" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
+    <xf numFmtId="0" fontId="3" fillId="3" borderId="0" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="3" fillId="4" borderId="0" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="3" fillId="5" borderId="0" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="3" fillId="6" borderId="0" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="4" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
   </cellXfs>
   <cellStyles count="1">
     <cellStyle name="Normal" xfId="0" builtinId="0" hidden="0"/>
@@ -155,131 +185,6 @@
     </indexedColors>
   </colors>
 </styleSheet>
-</file>
-
-<file path=xl/charts/chart1.xml><?xml version="1.0" encoding="utf-8"?>
-<chartSpace xmlns="http://schemas.openxmlformats.org/drawingml/2006/chart">
-  <style val="10"/>
-  <chart>
-    <title>
-      <tx>
-        <rich>
-          <a:bodyPr xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main"/>
-          <a:p xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main">
-            <a:pPr>
-              <a:defRPr/>
-            </a:pPr>
-            <a:r>
-              <a:t>Peer Benchmarking</a:t>
-            </a:r>
-          </a:p>
-        </rich>
-      </tx>
-    </title>
-    <plotArea>
-      <barChart>
-        <barDir val="bar"/>
-        <grouping val="clustered"/>
-        <ser>
-          <idx val="0"/>
-          <order val="0"/>
-          <tx>
-            <strRef>
-              <f>'Peer_Benchmarking'!C1</f>
-            </strRef>
-          </tx>
-          <spPr>
-            <a:ln xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main">
-              <a:prstDash val="solid"/>
-            </a:ln>
-          </spPr>
-          <cat>
-            <numRef>
-              <f>'Peer_Benchmarking'!$A$2:$A$7</f>
-            </numRef>
-          </cat>
-          <val>
-            <numRef>
-              <f>'Peer_Benchmarking'!$C$2:$C$7</f>
-            </numRef>
-          </val>
-        </ser>
-        <gapWidth val="150"/>
-        <axId val="10"/>
-        <axId val="100"/>
-      </barChart>
-      <catAx>
-        <axId val="10"/>
-        <scaling>
-          <orientation val="minMax"/>
-        </scaling>
-        <axPos val="l"/>
-        <majorTickMark val="none"/>
-        <minorTickMark val="none"/>
-        <crossAx val="100"/>
-        <lblOffset val="100"/>
-      </catAx>
-      <valAx>
-        <axId val="100"/>
-        <scaling>
-          <orientation val="minMax"/>
-        </scaling>
-        <axPos val="l"/>
-        <majorGridlines/>
-        <title>
-          <tx>
-            <rich>
-              <a:bodyPr xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main"/>
-              <a:p xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main">
-                <a:pPr>
-                  <a:defRPr/>
-                </a:pPr>
-                <a:r>
-                  <a:t>Multiple (x)</a:t>
-                </a:r>
-              </a:p>
-            </rich>
-          </tx>
-        </title>
-        <majorTickMark val="none"/>
-        <minorTickMark val="none"/>
-        <crossAx val="10"/>
-      </valAx>
-    </plotArea>
-    <legend>
-      <legendPos val="r"/>
-    </legend>
-    <plotVisOnly val="1"/>
-    <dispBlanksAs val="gap"/>
-  </chart>
-</chartSpace>
-</file>
-
-<file path=xl/drawings/drawing1.xml><?xml version="1.0" encoding="utf-8"?>
-<wsDr xmlns="http://schemas.openxmlformats.org/drawingml/2006/spreadsheetDrawing">
-  <oneCellAnchor>
-    <from>
-      <col>5</col>
-      <colOff>0</colOff>
-      <row>1</row>
-      <rowOff>0</rowOff>
-    </from>
-    <ext cx="5400000" cy="2700000"/>
-    <graphicFrame>
-      <nvGraphicFramePr>
-        <cNvPr id="1" name="Chart 1"/>
-        <cNvGraphicFramePr/>
-      </nvGraphicFramePr>
-      <xfrm/>
-      <a:graphic xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main">
-        <a:graphicData uri="http://schemas.openxmlformats.org/drawingml/2006/chart">
-          <c:chart xmlns:c="http://schemas.openxmlformats.org/drawingml/2006/chart" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:id="rId1"/>
-        </a:graphicData>
-      </a:graphic>
-    </graphicFrame>
-    <clientData/>
-  </oneCellAnchor>
-</wsDr>
 </file>
 
 <file path=xl/theme/theme1.xml><?xml version="1.0" encoding="utf-8"?>
@@ -571,213 +476,588 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:D7"/>
+  <dimension ref="A1:L21"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
-    <col width="17" customWidth="1" min="1" max="1"/>
-    <col width="19" customWidth="1" min="2" max="2"/>
-    <col width="14" customWidth="1" min="3" max="3"/>
+    <col width="8" customWidth="1" min="1" max="1"/>
+    <col width="33" customWidth="1" min="2" max="2"/>
+    <col width="8" customWidth="1" min="3" max="3"/>
     <col width="12" customWidth="1" min="4" max="4"/>
+    <col width="12" customWidth="1" min="5" max="5"/>
+    <col width="8" customWidth="1" min="6" max="6"/>
+    <col width="8" customWidth="1" min="7" max="7"/>
+    <col width="8" customWidth="1" min="8" max="8"/>
+    <col width="13" customWidth="1" min="9" max="9"/>
+    <col width="8" customWidth="1" min="10" max="10"/>
+    <col width="11" customWidth="1" min="11" max="11"/>
+    <col width="10" customWidth="1" min="12" max="12"/>
   </cols>
   <sheetData>
-    <row r="1">
-      <c r="A1" s="1" t="inlineStr">
-        <is>
-          <t>Company</t>
-        </is>
-      </c>
-      <c r="B1" s="1" t="inlineStr">
-        <is>
-          <t>Logo_Path</t>
-        </is>
-      </c>
-      <c r="C1" s="1" t="inlineStr">
-        <is>
-          <t>Metric_Value</t>
-        </is>
-      </c>
-      <c r="D1" s="1" t="inlineStr">
-        <is>
-          <t>Is_Subject</t>
-        </is>
-      </c>
-    </row>
+    <row r="1"/>
     <row r="2">
-      <c r="A2" s="2" t="inlineStr">
-        <is>
-          <t>Peer A</t>
-        </is>
-      </c>
-      <c r="B2" s="2" t="inlineStr">
-        <is>
-          <t>logos/peer_a.png</t>
-        </is>
-      </c>
-      <c r="C2" s="2" t="n">
-        <v>23.8</v>
-      </c>
-      <c r="D2" s="2" t="b">
-        <v>0</v>
-      </c>
-    </row>
-    <row r="3">
-      <c r="A3" s="3" t="inlineStr">
-        <is>
-          <t>Peer B</t>
-        </is>
-      </c>
-      <c r="B3" s="3" t="inlineStr">
-        <is>
-          <t>logos/peer_b.png</t>
-        </is>
-      </c>
-      <c r="C3" s="3" t="n">
-        <v>22.4</v>
-      </c>
-      <c r="D3" s="3" t="b">
-        <v>0</v>
-      </c>
-    </row>
+      <c r="B2" s="1" t="inlineStr">
+        <is>
+          <t>SaaS Peer Benchmarking Analysis</t>
+        </is>
+      </c>
+    </row>
+    <row r="3"/>
     <row r="4">
-      <c r="A4" s="2" t="inlineStr">
-        <is>
-          <t>Peer C</t>
-        </is>
-      </c>
+      <c r="A4" t="inlineStr"/>
       <c r="B4" s="2" t="inlineStr">
         <is>
-          <t>logos/peer_c.png</t>
-        </is>
-      </c>
-      <c r="C4" s="2" t="n">
-        <v>20.2</v>
-      </c>
-      <c r="D4" s="2" t="b">
-        <v>0</v>
-      </c>
-    </row>
-    <row r="5">
-      <c r="A5" s="3" t="inlineStr">
-        <is>
-          <t>Subject Company</t>
-        </is>
-      </c>
-      <c r="B5" s="3" t="inlineStr">
-        <is>
-          <t>logos/subject.png</t>
-        </is>
-      </c>
-      <c r="C5" s="3" t="n">
-        <v>18.2</v>
-      </c>
-      <c r="D5" s="3" t="b">
-        <v>1</v>
-      </c>
-    </row>
+          <t>Metric</t>
+        </is>
+      </c>
+      <c r="C4" s="3" t="inlineStr">
+        <is>
+          <t>Bottom</t>
+        </is>
+      </c>
+      <c r="D4" s="4" t="inlineStr">
+        <is>
+          <t>2nd</t>
+        </is>
+      </c>
+      <c r="E4" s="5" t="inlineStr">
+        <is>
+          <t>3rd</t>
+        </is>
+      </c>
+      <c r="F4" s="6" t="inlineStr">
+        <is>
+          <t>Top</t>
+        </is>
+      </c>
+      <c r="G4" s="2" t="inlineStr"/>
+      <c r="H4" s="2" t="inlineStr">
+        <is>
+          <t>Actual</t>
+        </is>
+      </c>
+      <c r="I4" s="2" t="inlineStr">
+        <is>
+          <t>Quartile</t>
+        </is>
+      </c>
+      <c r="J4" s="2" t="inlineStr"/>
+      <c r="K4" s="2" t="inlineStr">
+        <is>
+          <t>Projected</t>
+        </is>
+      </c>
+      <c r="L4" s="2" t="inlineStr">
+        <is>
+          <t>Quartile</t>
+        </is>
+      </c>
+    </row>
+    <row r="5"/>
     <row r="6">
-      <c r="A6" s="2" t="inlineStr">
-        <is>
-          <t>Peer D</t>
-        </is>
-      </c>
-      <c r="B6" s="2" t="inlineStr">
-        <is>
-          <t>logos/peer_d.png</t>
-        </is>
-      </c>
-      <c r="C6" s="2" t="n">
-        <v>16.7</v>
-      </c>
-      <c r="D6" s="2" t="b">
-        <v>0</v>
+      <c r="B6" s="7" t="inlineStr">
+        <is>
+          <t>Growth</t>
+        </is>
       </c>
     </row>
     <row r="7">
-      <c r="A7" s="3" t="inlineStr">
-        <is>
-          <t>Peer E</t>
-        </is>
-      </c>
-      <c r="B7" s="3" t="inlineStr">
-        <is>
-          <t>logos/peer_e.png</t>
-        </is>
-      </c>
-      <c r="C7" s="3" t="n">
-        <v>13.8</v>
-      </c>
-      <c r="D7" s="3" t="b">
-        <v>0</v>
-      </c>
-    </row>
-  </sheetData>
-  <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
-  <drawing xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:id="rId1"/>
-</worksheet>
-</file>
-
-<file path=xl/worksheets/sheet2.xml><?xml version="1.0" encoding="utf-8"?>
-<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
-  <sheetPr>
-    <outlinePr summaryBelow="1" summaryRight="1"/>
-    <pageSetUpPr/>
-  </sheetPr>
-  <dimension ref="A1:A10"/>
-  <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
-  <sheetData>
-    <row r="1">
-      <c r="A1" s="4" t="inlineStr">
-        <is>
-          <t>PEER BENCHMARKING TEMPLATE</t>
-        </is>
-      </c>
-    </row>
-    <row r="3">
-      <c r="A3" t="inlineStr">
-        <is>
-          <t>Columns:</t>
-        </is>
-      </c>
-    </row>
-    <row r="4">
-      <c r="A4" t="inlineStr">
-        <is>
-          <t>- Company: Peer company name</t>
-        </is>
-      </c>
-    </row>
-    <row r="5">
-      <c r="A5" t="inlineStr">
-        <is>
-          <t>- Logo_Path: Optional path to company logo</t>
-        </is>
-      </c>
-    </row>
-    <row r="6">
-      <c r="A6" t="inlineStr">
-        <is>
-          <t>- Metric_Value: The metric being compared (multiple, %, etc.)</t>
-        </is>
-      </c>
-    </row>
-    <row r="7">
-      <c r="A7" t="inlineStr">
-        <is>
-          <t>- Is_Subject: TRUE for your company (will be highlighted green)</t>
-        </is>
-      </c>
+      <c r="B7" t="inlineStr">
+        <is>
+          <t>ARR Growth (YoY)</t>
+        </is>
+      </c>
+      <c r="C7" t="inlineStr">
+        <is>
+          <t>&lt;9%</t>
+        </is>
+      </c>
+      <c r="D7" t="inlineStr">
+        <is>
+          <t>9-13%</t>
+        </is>
+      </c>
+      <c r="E7" t="inlineStr">
+        <is>
+          <t>13-21%</t>
+        </is>
+      </c>
+      <c r="F7" t="inlineStr">
+        <is>
+          <t>&gt;21%</t>
+        </is>
+      </c>
+      <c r="G7" t="inlineStr">
+        <is>
+          <t>35%</t>
+        </is>
+      </c>
+      <c r="H7" t="inlineStr">
+        <is>
+          <t>Top</t>
+        </is>
+      </c>
+      <c r="I7" t="inlineStr">
+        <is>
+          <t>28%</t>
+        </is>
+      </c>
+      <c r="J7" t="inlineStr">
+        <is>
+          <t>Top</t>
+        </is>
+      </c>
+    </row>
+    <row r="8">
+      <c r="B8" t="inlineStr"/>
+      <c r="C8" t="inlineStr"/>
+      <c r="D8" t="inlineStr"/>
+      <c r="E8" t="inlineStr"/>
+      <c r="F8" t="inlineStr"/>
+      <c r="G8" t="inlineStr"/>
+      <c r="H8" t="inlineStr"/>
+      <c r="I8" t="inlineStr"/>
+      <c r="J8" t="inlineStr"/>
     </row>
     <row r="9">
-      <c r="A9" t="inlineStr">
-        <is>
-          <t>Chart will show horizontal bars sorted by value.</t>
-        </is>
-      </c>
+      <c r="B9" s="7" t="inlineStr">
+        <is>
+          <t>Retention</t>
+        </is>
+      </c>
+      <c r="C9" t="inlineStr"/>
+      <c r="D9" t="inlineStr"/>
+      <c r="E9" t="inlineStr"/>
+      <c r="F9" t="inlineStr"/>
+      <c r="G9" t="inlineStr"/>
+      <c r="H9" t="inlineStr"/>
+      <c r="I9" t="inlineStr"/>
+      <c r="J9" t="inlineStr"/>
     </row>
     <row r="10">
-      <c r="A10" t="inlineStr">
-        <is>
-          <t>Subject company bar will be green, peers gray.</t>
+      <c r="B10" t="inlineStr">
+        <is>
+          <t>Net Dollar Retention</t>
+        </is>
+      </c>
+      <c r="C10" t="inlineStr">
+        <is>
+          <t>&lt;97%</t>
+        </is>
+      </c>
+      <c r="D10" t="inlineStr">
+        <is>
+          <t>97-105%</t>
+        </is>
+      </c>
+      <c r="E10" t="inlineStr">
+        <is>
+          <t>105-115%</t>
+        </is>
+      </c>
+      <c r="F10" t="inlineStr">
+        <is>
+          <t>&gt;115%</t>
+        </is>
+      </c>
+      <c r="G10" t="inlineStr">
+        <is>
+          <t>118%</t>
+        </is>
+      </c>
+      <c r="H10" t="inlineStr">
+        <is>
+          <t>Top</t>
+        </is>
+      </c>
+      <c r="I10" t="inlineStr">
+        <is>
+          <t>115%</t>
+        </is>
+      </c>
+      <c r="J10" t="inlineStr">
+        <is>
+          <t>Top</t>
+        </is>
+      </c>
+    </row>
+    <row r="11">
+      <c r="B11" t="inlineStr">
+        <is>
+          <t>Gross Dollar Retention</t>
+        </is>
+      </c>
+      <c r="C11" t="inlineStr">
+        <is>
+          <t>&lt;78%</t>
+        </is>
+      </c>
+      <c r="D11" t="inlineStr">
+        <is>
+          <t>78-85%</t>
+        </is>
+      </c>
+      <c r="E11" t="inlineStr">
+        <is>
+          <t>85-90%</t>
+        </is>
+      </c>
+      <c r="F11" t="inlineStr">
+        <is>
+          <t>&gt;90%</t>
+        </is>
+      </c>
+      <c r="G11" t="inlineStr">
+        <is>
+          <t>92%</t>
+        </is>
+      </c>
+      <c r="H11" t="inlineStr">
+        <is>
+          <t>Top</t>
+        </is>
+      </c>
+      <c r="I11" t="inlineStr">
+        <is>
+          <t>91%</t>
+        </is>
+      </c>
+      <c r="J11" t="inlineStr">
+        <is>
+          <t>Top</t>
+        </is>
+      </c>
+    </row>
+    <row r="12">
+      <c r="B12" t="inlineStr"/>
+      <c r="C12" t="inlineStr"/>
+      <c r="D12" t="inlineStr"/>
+      <c r="E12" t="inlineStr"/>
+      <c r="F12" t="inlineStr"/>
+      <c r="G12" t="inlineStr"/>
+      <c r="H12" t="inlineStr"/>
+      <c r="I12" t="inlineStr"/>
+      <c r="J12" t="inlineStr"/>
+    </row>
+    <row r="13">
+      <c r="B13" s="7" t="inlineStr">
+        <is>
+          <t>Efficiency</t>
+        </is>
+      </c>
+      <c r="C13" t="inlineStr"/>
+      <c r="D13" t="inlineStr"/>
+      <c r="E13" t="inlineStr"/>
+      <c r="F13" t="inlineStr"/>
+      <c r="G13" t="inlineStr"/>
+      <c r="H13" t="inlineStr"/>
+      <c r="I13" t="inlineStr"/>
+      <c r="J13" t="inlineStr"/>
+    </row>
+    <row r="14">
+      <c r="B14" t="inlineStr">
+        <is>
+          <t>Magic Number</t>
+        </is>
+      </c>
+      <c r="C14" t="inlineStr">
+        <is>
+          <t>&lt;0.37x</t>
+        </is>
+      </c>
+      <c r="D14" t="inlineStr">
+        <is>
+          <t>0.37-0.47x</t>
+        </is>
+      </c>
+      <c r="E14" t="inlineStr">
+        <is>
+          <t>0.47-0.72x</t>
+        </is>
+      </c>
+      <c r="F14" t="inlineStr">
+        <is>
+          <t>&gt;0.72x</t>
+        </is>
+      </c>
+      <c r="G14" t="inlineStr">
+        <is>
+          <t>0.85x</t>
+        </is>
+      </c>
+      <c r="H14" t="inlineStr">
+        <is>
+          <t>Top</t>
+        </is>
+      </c>
+      <c r="I14" t="inlineStr">
+        <is>
+          <t>0.65x</t>
+        </is>
+      </c>
+      <c r="J14" t="inlineStr">
+        <is>
+          <t>3rd</t>
+        </is>
+      </c>
+    </row>
+    <row r="15">
+      <c r="B15" t="inlineStr">
+        <is>
+          <t>LTV/CAC</t>
+        </is>
+      </c>
+      <c r="C15" t="inlineStr">
+        <is>
+          <t>&lt;2.0x</t>
+        </is>
+      </c>
+      <c r="D15" t="inlineStr">
+        <is>
+          <t>2.0-3.0x</t>
+        </is>
+      </c>
+      <c r="E15" t="inlineStr">
+        <is>
+          <t>3.0-4.5x</t>
+        </is>
+      </c>
+      <c r="F15" t="inlineStr">
+        <is>
+          <t>&gt;4.5x</t>
+        </is>
+      </c>
+      <c r="G15" t="inlineStr">
+        <is>
+          <t>3.8x</t>
+        </is>
+      </c>
+      <c r="H15" t="inlineStr">
+        <is>
+          <t>3rd</t>
+        </is>
+      </c>
+      <c r="I15" t="inlineStr">
+        <is>
+          <t>4.2x</t>
+        </is>
+      </c>
+      <c r="J15" t="inlineStr">
+        <is>
+          <t>3rd</t>
+        </is>
+      </c>
+    </row>
+    <row r="16">
+      <c r="B16" t="inlineStr">
+        <is>
+          <t>CAC Payback (months)</t>
+        </is>
+      </c>
+      <c r="C16" t="inlineStr">
+        <is>
+          <t>&gt;44</t>
+        </is>
+      </c>
+      <c r="D16" t="inlineStr">
+        <is>
+          <t>32-44</t>
+        </is>
+      </c>
+      <c r="E16" t="inlineStr">
+        <is>
+          <t>23-32</t>
+        </is>
+      </c>
+      <c r="F16" t="inlineStr">
+        <is>
+          <t>&lt;23</t>
+        </is>
+      </c>
+      <c r="G16" t="inlineStr">
+        <is>
+          <t>28</t>
+        </is>
+      </c>
+      <c r="H16" t="inlineStr">
+        <is>
+          <t>3rd</t>
+        </is>
+      </c>
+      <c r="I16" t="inlineStr">
+        <is>
+          <t>25</t>
+        </is>
+      </c>
+      <c r="J16" t="inlineStr">
+        <is>
+          <t>3rd</t>
+        </is>
+      </c>
+    </row>
+    <row r="17">
+      <c r="B17" t="inlineStr">
+        <is>
+          <t>Burn Multiple</t>
+        </is>
+      </c>
+      <c r="C17" t="inlineStr">
+        <is>
+          <t>&gt;3.5x</t>
+        </is>
+      </c>
+      <c r="D17" t="inlineStr">
+        <is>
+          <t>2.5-3.5x</t>
+        </is>
+      </c>
+      <c r="E17" t="inlineStr">
+        <is>
+          <t>1.8-2.5x</t>
+        </is>
+      </c>
+      <c r="F17" t="inlineStr">
+        <is>
+          <t>&lt;1.8x</t>
+        </is>
+      </c>
+      <c r="G17" t="inlineStr">
+        <is>
+          <t>1.5x</t>
+        </is>
+      </c>
+      <c r="H17" t="inlineStr">
+        <is>
+          <t>Top</t>
+        </is>
+      </c>
+      <c r="I17" t="inlineStr">
+        <is>
+          <t>Pos. EBITDA</t>
+        </is>
+      </c>
+      <c r="J17" t="inlineStr">
+        <is>
+          <t>Top</t>
+        </is>
+      </c>
+    </row>
+    <row r="18">
+      <c r="B18" t="inlineStr"/>
+      <c r="C18" t="inlineStr"/>
+      <c r="D18" t="inlineStr"/>
+      <c r="E18" t="inlineStr"/>
+      <c r="F18" t="inlineStr"/>
+      <c r="G18" t="inlineStr"/>
+      <c r="H18" t="inlineStr"/>
+      <c r="I18" t="inlineStr"/>
+      <c r="J18" t="inlineStr"/>
+    </row>
+    <row r="19">
+      <c r="B19" s="7" t="inlineStr">
+        <is>
+          <t>Profitability</t>
+        </is>
+      </c>
+      <c r="C19" t="inlineStr"/>
+      <c r="D19" t="inlineStr"/>
+      <c r="E19" t="inlineStr"/>
+      <c r="F19" t="inlineStr"/>
+      <c r="G19" t="inlineStr"/>
+      <c r="H19" t="inlineStr"/>
+      <c r="I19" t="inlineStr"/>
+      <c r="J19" t="inlineStr"/>
+    </row>
+    <row r="20">
+      <c r="B20" t="inlineStr">
+        <is>
+          <t>Gross Margin</t>
+        </is>
+      </c>
+      <c r="C20" t="inlineStr">
+        <is>
+          <t>&lt;73%</t>
+        </is>
+      </c>
+      <c r="D20" t="inlineStr">
+        <is>
+          <t>73-78%</t>
+        </is>
+      </c>
+      <c r="E20" t="inlineStr">
+        <is>
+          <t>78-82%</t>
+        </is>
+      </c>
+      <c r="F20" t="inlineStr">
+        <is>
+          <t>&gt;82%</t>
+        </is>
+      </c>
+      <c r="G20" t="inlineStr">
+        <is>
+          <t>85%</t>
+        </is>
+      </c>
+      <c r="H20" t="inlineStr">
+        <is>
+          <t>Top</t>
+        </is>
+      </c>
+      <c r="I20" t="inlineStr">
+        <is>
+          <t>86%</t>
+        </is>
+      </c>
+      <c r="J20" t="inlineStr">
+        <is>
+          <t>Top</t>
+        </is>
+      </c>
+    </row>
+    <row r="21">
+      <c r="B21" t="inlineStr">
+        <is>
+          <t>Rule of 40</t>
+        </is>
+      </c>
+      <c r="C21" t="inlineStr">
+        <is>
+          <t>&lt;28%</t>
+        </is>
+      </c>
+      <c r="D21" t="inlineStr">
+        <is>
+          <t>28-37%</t>
+        </is>
+      </c>
+      <c r="E21" t="inlineStr">
+        <is>
+          <t>37-45%</t>
+        </is>
+      </c>
+      <c r="F21" t="inlineStr">
+        <is>
+          <t>&gt;45%</t>
+        </is>
+      </c>
+      <c r="G21" t="inlineStr">
+        <is>
+          <t>42%</t>
+        </is>
+      </c>
+      <c r="H21" t="inlineStr">
+        <is>
+          <t>3rd</t>
+        </is>
+      </c>
+      <c r="I21" t="inlineStr">
+        <is>
+          <t>38%</t>
+        </is>
+      </c>
+      <c r="J21" t="inlineStr">
+        <is>
+          <t>3rd</t>
         </is>
       </c>
     </row>
